--- a/artfynd/A 5807-2024 artfynd.xlsx
+++ b/artfynd/A 5807-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5807-2024 artfynd.xlsx
+++ b/artfynd/A 5807-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>88477791</v>
       </c>
       <c r="B2" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,7 +695,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404470.630460004</v>
+        <v>404471</v>
       </c>
       <c r="R2" t="n">
-        <v>6448174.507967668</v>
+        <v>6448175</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +747,9 @@
           <t>1983-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1983-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
